--- a/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
+++ b/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\indst\SoCiIEPTtB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\indst\SoCiIEPTtB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D170B4D2-127F-4FC7-9E13-42171A432FA7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D87643-3FBD-4818-AB4B-E532AC1F3B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="915" windowWidth="24090" windowHeight="16245" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
+    <workbookView xWindow="35730" yWindow="4035" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>SoCiIEPTtB Share of Change in Industry Expenses Passed Through to Buyers</t>
   </si>
@@ -138,10 +138,82 @@
     <t>Unit: dimensionless (% passthrough)</t>
   </si>
   <si>
-    <t>Share of expenses</t>
-  </si>
-  <si>
     <t>Paid by consumers</t>
+  </si>
+  <si>
+    <t>agriculture and forestry 01T03</t>
+  </si>
+  <si>
+    <t>coal mining 05</t>
+  </si>
+  <si>
+    <t>oil and gas extraction 06</t>
+  </si>
+  <si>
+    <t>other mining and quarrying 07T08</t>
+  </si>
+  <si>
+    <t>food beverage and tobacco 10T12</t>
+  </si>
+  <si>
+    <t>textiles apparel and leather 13T15</t>
+  </si>
+  <si>
+    <t>wood products 16</t>
+  </si>
+  <si>
+    <t>pulp paper and printing 17T18</t>
+  </si>
+  <si>
+    <t>refined petroleum and coke 19</t>
+  </si>
+  <si>
+    <t>chemicals 20</t>
+  </si>
+  <si>
+    <t>rubber and plastic products 22</t>
+  </si>
+  <si>
+    <t>glass and glass products 231</t>
+  </si>
+  <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
+    <t>iron and steel 241</t>
+  </si>
+  <si>
+    <t>other metals 242</t>
+  </si>
+  <si>
+    <t>metal products except machinery and vehicles 25</t>
+  </si>
+  <si>
+    <t>computers and electronics 26</t>
+  </si>
+  <si>
+    <t>appliances and electrical equipment 27</t>
+  </si>
+  <si>
+    <t>other machinery 28</t>
+  </si>
+  <si>
+    <t>road vehicles 29</t>
+  </si>
+  <si>
+    <t>nonroad vehicles 30</t>
+  </si>
+  <si>
+    <t>other manufacturing 31T33</t>
+  </si>
+  <si>
+    <t>energy pipelines and gas processing 352T353</t>
+  </si>
+  <si>
+    <t>water and waste 36T39</t>
+  </si>
+  <si>
+    <t>construction 41T43</t>
   </si>
 </sst>
 </file>
@@ -202,14 +274,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -230,9 +301,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -270,7 +341,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -376,7 +447,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -518,7 +589,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -527,17 +598,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA9904B-1EB4-4402-820D-BB1B47048552}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="91.140625" customWidth="1"/>
+    <col min="2" max="2" width="91.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,157 +616,157 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1</v>
       </c>
@@ -717,27 +788,243 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="35.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
       <c r="B2">
-        <f>About!A42</f>
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25">
+        <f>About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26">
+        <f>About!A$42</f>
         <v>1</v>
       </c>
     </row>

--- a/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
+++ b/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\indst\SoCiIEPTtB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/indst/indst/SoCiIEPTtB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D87643-3FBD-4818-AB4B-E532AC1F3B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D170B4D2-127F-4FC7-9E13-42171A432FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60DC8029-7F95-4D22-9229-5CF20383B2F0}"/>
   <bookViews>
-    <workbookView xWindow="35730" yWindow="4035" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="SoCiIEPTtB" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,18 +48,18 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>Anna Milanez, OECD</t>
+  </si>
+  <si>
+    <t>Legal tax liability, legal remittance responsibility and tax incidence: Three dimensions of business taxation</t>
+  </si>
+  <si>
+    <t>https://www.oecd-ilibrary.org/deliver/e7ced3ea-en.pdf?itemId=%2Fcontent%2Fpaper%2Fe7ced3ea-en&amp;mimeType=pdf</t>
+  </si>
+  <si>
     <t>Pages 40-41</t>
   </si>
   <si>
-    <t>Anna Milanez, OECD</t>
-  </si>
-  <si>
-    <t>https://www.oecd-ilibrary.org/deliver/e7ced3ea-en.pdf?itemId=%2Fcontent%2Fpaper%2Fe7ced3ea-en&amp;mimeType=pdf</t>
-  </si>
-  <si>
-    <t>Legal tax liability, legal remittance responsibility and tax incidence: Three dimensions of business taxation</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -114,6 +120,9 @@
     <t>pass-through (i.e., full incidence of indirect taxation on consumers) is a reasonable estimate"</t>
   </si>
   <si>
+    <t>Benedek, de Mooij, Keen, &amp; Wingender (2015)</t>
+  </si>
+  <si>
     <t>This is difficult to estimate, because it depends on minutiae of the tax design, and likely also the tax base</t>
   </si>
   <si>
@@ -121,9 +130,6 @@
   </si>
   <si>
     <t>geographies or industries.</t>
-  </si>
-  <si>
-    <t>Benedek, de Mooij, Keen, &amp; Wingender (2015)</t>
   </si>
   <si>
     <t>Accordingly, we adopt the recommendation of the Benedek, de Mooij, Keen, &amp; Wingender (2015) study</t>
@@ -298,6 +304,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="SoCiIEPTtB"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="42">
+          <cell r="A42">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -598,175 +628,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA9904B-1EB4-4402-820D-BB1B47048552}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="91.1796875" customWidth="1"/>
+    <col min="2" max="2" width="91.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1</v>
       </c>
@@ -789,13 +819,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -803,232 +833,426 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
       <c r="B3">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
       <c r="B4">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
       <c r="B5">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
       <c r="B6">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
       <c r="B7">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
       <c r="B8">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
       <c r="B9">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
       <c r="B10">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
       <c r="B11">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
       <c r="B12">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
       <c r="B13">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
       <c r="B14">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
       <c r="B15">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
       <c r="B16">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
       <c r="B17">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
       <c r="B18">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
       <c r="B20">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
       <c r="B21">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
       <c r="B22">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
       <c r="B23">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
       <c r="B24">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
       <c r="B25">
-        <f>About!A$42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <f>[1]About!A$42</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
       <c r="B26">
-        <f>About!A$42</f>
+        <f>[1]About!A$42</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7C4CA4A-BBC7-46F7-8F1C-A0AD28FB94F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2CB3DE8-2498-415A-8B1C-FCA36C069692}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92316F2A-4927-4488-ADEE-9327789FFFE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>